--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104560_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104560_W12.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.781</v>
+        <v>4.3404</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9809</v>
+        <v>2.1258</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8</v>
+        <v>2.2145</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5589</v>
+        <v>2.5563</v>
       </c>
       <c r="H2" t="n">
-        <v>0.821</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7379</v>
+        <v>1.7322</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4186</v>
+        <v>2.3817</v>
       </c>
       <c r="K2" t="n">
-        <v>2.019</v>
+        <v>2.0027</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3997</v>
+        <v>0.3789</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1403</v>
+        <v>0.1746</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.198</v>
+        <v>-1.1786</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3382</v>
+        <v>1.3532</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.1389</v>
+        <v>-1.5817</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5303</v>
+        <v>-1.3453</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6085</v>
+        <v>-0.2364</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6689</v>
+        <v>1.5773</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4388</v>
+        <v>0.5835</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2301</v>
+        <v>0.9938</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6051</v>
+        <v>1.6258</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0532</v>
+        <v>1.0622</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5636</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2112</v>
+        <v>2.1959</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4648</v>
+        <v>1.4511</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6061</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4116</v>
+        <v>-0.389</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5337</v>
+        <v>-1.634</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.8086</v>
+        <v>-1.6241</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2749</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1833</v>
+        <v>-0.3956</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1413</v>
+        <v>-1.1531</v>
       </c>
       <c r="F4" t="n">
-        <v>0.958</v>
+        <v>0.7575</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.3719</v>
+        <v>-1.3609</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3696</v>
+        <v>-0.3568</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0023</v>
+        <v>-1.0041</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.4688</v>
+        <v>-1.4759</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M4" t="n">
-        <v>0.097</v>
+        <v>0.1149</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5846</v>
+        <v>-0.8071</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7652</v>
+        <v>-0.7667</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1805</v>
+        <v>-0.0403</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9524</v>
+        <v>-0.9014</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7099</v>
+        <v>-1.9852</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7575</v>
+        <v>1.0838</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7998</v>
+        <v>-0.9388</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9278</v>
+        <v>-2.2254</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1281</v>
+        <v>1.2866</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1828</v>
+        <v>-0.7699</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4067</v>
+        <v>-1.7074</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2239</v>
+        <v>0.9375</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.617</v>
+        <v>-0.1689</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5212</v>
+        <v>-0.518</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0958</v>
+        <v>0.3492</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1403</v>
+        <v>-1.4586</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6049</v>
+        <v>-1.2756</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7452</v>
+        <v>-0.183</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7071</v>
+        <v>2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.639</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9835</v>
+        <v>-1.0336</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8212</v>
+        <v>-0.8289</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1622</v>
+        <v>-0.2047</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7467</v>
+        <v>0.7595</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0403</v>
+        <v>0.0457</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7064</v>
+        <v>0.7139</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6607</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6234</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1018</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1839</v>
+        <v>-0.2483</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1639</v>
+        <v>0.1002</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>W. HOWARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3713</v>
+        <v>-1.6149</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1043</v>
+        <v>-3.3797</v>
       </c>
       <c r="F7" t="n">
-        <v>0.733</v>
+        <v>1.7648</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9223</v>
+        <v>-1.3608</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.2177</v>
+        <v>-1.0976</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2954</v>
+        <v>-0.2633</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7212</v>
+        <v>-1.5235</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.6806</v>
+        <v>-1.4414</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9594</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2011</v>
+        <v>0.1627</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5371</v>
+        <v>0.3438</v>
       </c>
       <c r="O7" t="n">
-        <v>0.336</v>
+        <v>-0.1811</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9538</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4608</v>
+        <v>-0.718</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.493</v>
+        <v>-0.219</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. HOWARD</t>
+          <t>J. PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4096</v>
+        <v>-1.6317</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.55</v>
+        <v>-1.3279</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1404</v>
+        <v>-0.3039</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3772</v>
+        <v>-0.105</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1054</v>
+        <v>1.2727</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2718</v>
+        <v>-1.3778</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5115</v>
+        <v>0.4522</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4342</v>
+        <v>1.9198</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-1.4676</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1343</v>
+        <v>-0.5573</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3288</v>
+        <v>-0.6471</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1945</v>
+        <v>0.0898</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7129</v>
+        <v>-1.1382</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9043</v>
+        <v>-1.1152</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1914</v>
+        <v>-0.0229</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.4733</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. PEREZ</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9942</v>
+        <v>-1.7819</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2832</v>
+        <v>-2.1456</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.711</v>
+        <v>0.3637</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1007</v>
+        <v>-1.7808</v>
       </c>
       <c r="H9" t="n">
-        <v>1.28</v>
+        <v>-1.9245</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3807</v>
+        <v>0.1437</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4818</v>
+        <v>-1.1975</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9426</v>
+        <v>-1.4209</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4608</v>
+        <v>0.2234</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5825</v>
+        <v>-0.5833</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6626</v>
+        <v>-0.5036</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>2.2763</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5098</v>
+        <v>-0.7036</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.113</v>
+        <v>-1.0085</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3968</v>
+        <v>0.3049</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6105</v>
+        <v>0.7025</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4822</v>
+        <v>2.3367</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3516</v>
+        <v>-2.2856</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4077</v>
+        <v>-0.7127</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0562</v>
+        <v>-1.5729</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2174</v>
+        <v>0.7429</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3724</v>
+        <v>-0.1123</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.845</v>
+        <v>0.8551</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7171</v>
+        <v>1.2712</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0693</v>
+        <v>0.348</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7864</v>
+        <v>0.9233</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5003</v>
+        <v>-0.5284</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4417</v>
+        <v>-0.4603</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0586</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4537</v>
+        <v>-1.209</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>-0.9061</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1028</v>
+        <v>-0.3028</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2292</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.3367</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.1075</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6294</v>
+        <v>-2.3467</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.674</v>
+        <v>-2.4165</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9554</v>
+        <v>0.0697</v>
       </c>
       <c r="G11" t="n">
-        <v>0.736</v>
+        <v>-1.2086</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.117</v>
+        <v>-0.3624</v>
       </c>
       <c r="I11" t="n">
-        <v>0.853</v>
+        <v>-0.8462</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2868</v>
+        <v>-0.7207</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3565</v>
+        <v>0.0689</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9302</v>
+        <v>-0.7896</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5507</v>
+        <v>-0.4879</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4735</v>
+        <v>-0.4314</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0772</v>
+        <v>-0.0565</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0415</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5488</v>
+        <v>-0.4553</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9043</v>
+        <v>-0.5576</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6445</v>
+        <v>0.1024</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2249</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3461</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.425399999999999</v>
+        <v>-6.0737</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.2719</v>
+        <v>-11.2403</v>
       </c>
       <c r="F12" t="n">
-        <v>4.8466</v>
+        <v>5.1663</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1426</v>
+        <v>-1.0704</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.9154</v>
+        <v>-2.8743</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7729</v>
+        <v>1.8037</v>
       </c>
       <c r="J12" t="n">
-        <v>1.457699999999999</v>
+        <v>1.2713</v>
       </c>
       <c r="K12" t="n">
-        <v>2.058</v>
+        <v>1.9447</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6004000000000002</v>
+        <v>-0.6735999999999996</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6001</v>
+        <v>-2.3419</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.9735</v>
+        <v>-4.8194</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3732</v>
+        <v>2.4775</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1343</v>
+        <v>-1.138300000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.8784</v>
+        <v>-15.9344</v>
       </c>
       <c r="R12" t="n">
-        <v>14.7441</v>
+        <v>14.7961</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.4798</v>
+        <v>-10.1728</v>
       </c>
       <c r="T12" t="n">
-        <v>-9.995699999999999</v>
+        <v>-9.665600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4841000000000001</v>
+        <v>-0.5067999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>6.3312</v>
+        <v>6.3076</v>
       </c>
       <c r="W12" t="n">
-        <v>13.1446</v>
+        <v>13.0886</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.8134</v>
+        <v>-6.781000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.7505</v>
+        <v>5.6856</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2657</v>
+        <v>4.2968</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4847</v>
+        <v>1.3888</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3797</v>
+        <v>3.3703</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7346</v>
+        <v>2.7206</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6451</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>3.046</v>
+        <v>3.0252</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9714</v>
+        <v>2.9508</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3337</v>
+        <v>0.3451</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9943</v>
+        <v>0.929</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0344</v>
+        <v>0.0926</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9599</v>
+        <v>0.8364</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4691</v>
+        <v>0.4757</v>
       </c>
       <c r="W13" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1699</v>
+        <v>-1.1585</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. CATE</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8732</v>
+        <v>2.9821</v>
       </c>
       <c r="E14" t="n">
-        <v>1.356</v>
+        <v>-0.5026</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5173</v>
+        <v>3.4847</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8883</v>
+        <v>3.3028</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4431</v>
+        <v>2.2357</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4452</v>
+        <v>1.0672</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9245</v>
+        <v>2.7533</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7753</v>
+        <v>1.7195</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1493</v>
+        <v>1.0339</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0362</v>
+        <v>0.5495</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3321</v>
+        <v>0.5162</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2959</v>
+        <v>0.0333</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-3.8697</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2383</v>
+        <v>1.0254</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2461</v>
+        <v>-0.0887</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9922</v>
+        <v>1.1142</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5463</v>
+        <v>0.7025</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1574</v>
+        <v>2.8149</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9578</v>
+        <v>1.4685</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1995</v>
+        <v>1.3464</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4303</v>
+        <v>1.6801</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6089</v>
+        <v>0.8609</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1786</v>
+        <v>0.8192</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5483</v>
+        <v>2.9533</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2007</v>
+        <v>0.6895</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.749</v>
+        <v>2.2638</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9787</v>
+        <v>-1.2731</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4082</v>
+        <v>0.1715</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5705</v>
+        <v>-1.4446</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1392</v>
+        <v>0.9778</v>
       </c>
       <c r="T15" t="n">
-        <v>1.733</v>
+        <v>-0.1189</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4062</v>
+        <v>1.0967</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5463</v>
+        <v>-0.2983</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5463</v>
+        <v>-0.2983</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>E. CATE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8019</v>
+        <v>2.6458</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3664</v>
+        <v>0.6218</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4355</v>
+        <v>2.024</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6692</v>
+        <v>0.8874</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.4342</v>
       </c>
       <c r="I16" t="n">
-        <v>0.821</v>
+        <v>0.4532</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9663</v>
+        <v>0.8999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6927</v>
+        <v>0.7509</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2736</v>
+        <v>0.1489</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2971</v>
+        <v>-0.0125</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1556</v>
+        <v>-0.3168</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4526</v>
+        <v>0.3043</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9811</v>
+        <v>2.0057</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2389</v>
+        <v>0.543</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>1.4627</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3021</v>
+        <v>-0.7025</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3021</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0757</v>
+        <v>2.5819</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6546</v>
+        <v>-1.0832</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7303</v>
+        <v>3.6651</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3445</v>
+        <v>1.0433</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2571</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0874</v>
+        <v>0.9655</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8212</v>
+        <v>-0.7087</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7552</v>
+        <v>0.0065</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0659</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5233</v>
+        <v>1.752</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5019</v>
+        <v>0.0713</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0214</v>
+        <v>1.6807</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8562</v>
+        <v>-0.4553</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.06560000000000001</v>
+        <v>1.4216</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3266</v>
+        <v>-0.077</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3923</v>
+        <v>1.4986</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7071</v>
+        <v>-1.4764</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6802</v>
+        <v>2.3269</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8885</v>
+        <v>-0.1116</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5687</v>
+        <v>2.4385</v>
       </c>
       <c r="G18" t="n">
-        <v>1.042</v>
+        <v>0.4317</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0823</v>
+        <v>0.6089</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9596</v>
+        <v>-0.1772</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6913</v>
+        <v>-0.5595</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0204</v>
+        <v>0.1929</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7117</v>
+        <v>-0.7524</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7333</v>
+        <v>0.9912</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0619</v>
+        <v>0.416</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6714</v>
+        <v>0.5752</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5286999999999999</v>
+        <v>1.3018</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9043</v>
+        <v>0.6756</v>
       </c>
       <c r="U18" t="n">
-        <v>1.433</v>
+        <v>0.6262</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4783</v>
+        <v>-0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.639</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.88</v>
+        <v>0.7385</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4214</v>
+        <v>1.2878</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5414</v>
+        <v>-0.5494</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0999</v>
+        <v>-1.0941</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3291</v>
+        <v>-1.3188</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2292</v>
+        <v>0.2247</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8821</v>
+        <v>0.8701</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9821</v>
+        <v>-1.9642</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.433</v>
+        <v>-1.4223</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.575</v>
+        <v>0.4283</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0998</v>
+        <v>-0.2164</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6747</v>
+        <v>0.6448</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9513</v>
+        <v>0.949</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1414</v>
+        <v>-0.1405</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2516</v>
+        <v>0.2331</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.6205</v>
+        <v>-2.8166</v>
       </c>
       <c r="F20" t="n">
-        <v>3.3689</v>
+        <v>3.0497</v>
       </c>
       <c r="G20" t="n">
-        <v>0.665</v>
+        <v>0.6662</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6277</v>
+        <v>0.6289</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0058</v>
+        <v>-0.008</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5412</v>
+        <v>1.5341</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6592</v>
+        <v>0.6741</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O20" t="n">
-        <v>1.5727</v>
+        <v>1.5793</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6052</v>
+        <v>1.0905</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9043</v>
+        <v>-0.077</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5095</v>
+        <v>1.1675</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2595</v>
+        <v>-0.1086</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0645</v>
+        <v>0.0535</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.195</v>
+        <v>-0.1622</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1413</v>
+        <v>-0.14</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2985</v>
+        <v>-0.2979</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1183</v>
+        <v>0.0313</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0004</v>
+        <v>-1.5935</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.4842</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9906</v>
+        <v>-1.1092</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0462</v>
+        <v>-1.0475</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7849</v>
+        <v>-0.7868000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2612</v>
+        <v>-0.2607</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6571</v>
+        <v>-0.6607</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L22" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3891</v>
+        <v>-0.3868</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9116</v>
+        <v>0.3159</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6472</v>
+        <v>0.1765</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2643</v>
+        <v>0.1394</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3063</v>
+        <v>-4.6953</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.9127</v>
+        <v>-5.3676</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.6723</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6428</v>
+        <v>-3.6544</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6521</v>
+        <v>-0.6601</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9908</v>
+        <v>-2.9943</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.6921</v>
+        <v>-2.726</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.154</v>
+        <v>-1.1763</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5381</v>
+        <v>-1.5497</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9507</v>
+        <v>-0.9284</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5019</v>
+        <v>0.5162</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8861</v>
+        <v>-0.2954</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9766</v>
+        <v>1.0096</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0734</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2341</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.9756</v>
+        <v>-7.189</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0631</v>
+        <v>-2.5291</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.9126</v>
+        <v>-4.6599</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.3463</v>
+        <v>-4.3753</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0777</v>
+        <v>-2.0847</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2685</v>
+        <v>-2.2905</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.5314</v>
+        <v>-3.5715</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1642</v>
+        <v>-1.1796</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.3672</v>
+        <v>-2.3919</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8149</v>
+        <v>-0.8037</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O24" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5314</v>
+        <v>0.2797</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6775</v>
+        <v>-0.0863</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1461</v>
+        <v>0.3659</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.098</v>
+        <v>-3.0934</v>
       </c>
       <c r="W24" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.6048</v>
+        <v>-5.5879</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.4255</v>
+        <v>6.422400000000003</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.846499999999999</v>
+        <v>-5.166500000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>11.2717</v>
+        <v>11.5888</v>
       </c>
       <c r="G25" t="n">
-        <v>1.142499999999999</v>
+        <v>1.070500000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>2.9155</v>
+        <v>2.8745</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.772800000000001</v>
+        <v>-1.8039</v>
       </c>
       <c r="J25" t="n">
-        <v>2.600300000000002</v>
+        <v>2.341899999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>4.9736</v>
+        <v>4.819299999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.3732</v>
+        <v>-2.477300000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.4578</v>
+        <v>-1.2712</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.058</v>
+        <v>-1.9449</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6004000000000005</v>
+        <v>0.6735000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-14.7443</v>
+        <v>-14.7961</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8784</v>
+        <v>15.9344</v>
       </c>
       <c r="S25" t="n">
-        <v>10.4797</v>
+        <v>10.5212</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4841</v>
+        <v>0.507</v>
       </c>
       <c r="U25" t="n">
-        <v>9.995699999999999</v>
+        <v>10.0143</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.331099999999999</v>
+        <v>-6.307599999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>6.8133</v>
+        <v>6.781000000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-13.1444</v>
+        <v>-13.0886</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104560_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104560_W12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1075</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-6.781000000000001</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.1585</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.2983</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1405</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.23</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-5.5879</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104560_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-13.0886</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
